--- a/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
+++ b/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -546,55 +556,61 @@
         <v>2010</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4449356199356199</v>
+        <v>0.519978354978355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3007399870535626</v>
+        <v>0.2998583294812446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4051125946677976</v>
+        <v>0.2231655884125293</v>
       </c>
       <c r="I2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.04049872052001606</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6086956521739131</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>0.5384615384615384</v>
       </c>
       <c r="P2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
       <c r="S2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.33</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -617,55 +633,61 @@
         <v>2010</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4466666666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3610321704439352</v>
+        <v>0.3695468312516368</v>
       </c>
       <c r="G3" t="n">
-        <v>0.261028</v>
+        <v>0.259828</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="I3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T3" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -688,55 +710,61 @@
         <v>2010</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4540362905068787</v>
+        <v>0.4547552447552448</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3309194445610046</v>
+        <v>0.3249748647212982</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6843586564064026</v>
+        <v>0.009690718725323677</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6086956521739131</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -759,55 +787,61 @@
         <v>2010</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4266666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3646127565245212</v>
+        <v>0.380859562264361</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3926556671239072</v>
+        <v>0.3959382376289337</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08150975529464062</v>
+        <v>0.1082939530143255</v>
       </c>
       <c r="I5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.06405386481620562</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P5" t="n">
         <v>0.6</v>
       </c>
-      <c r="N5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.1</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2266666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1633333333333333</v>
+        <v>0.46</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="6">
@@ -839,46 +873,52 @@
         <v>0.3682919642501296</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.4208144796380091</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -901,55 +941,61 @@
         <v>2010</v>
       </c>
       <c r="E7" t="n">
-        <v>0.62</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5086363636363637</v>
+        <v>0.4906788380701425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3275847922554616</v>
+        <v>0.3586356286202021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7893669792601311</v>
+        <v>0.01672838630672052</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R7" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.29</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2933333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2966666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2011</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6723809523809523</v>
+        <v>0.6757142857142856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2295154823327183</v>
+        <v>0.2264339472405482</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5466160452390791</v>
+        <v>0.04049872052001606</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0.55057275498641</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>0.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.29</v>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +1095,61 @@
         <v>2011</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6295921184079079</v>
+        <v>0.731231867547657</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2137274613314862</v>
+        <v>0.2034431140401223</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5138667912590348</v>
+        <v>0.22</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>0.54081673076076</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.1466666666666667</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1233333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +1172,61 @@
         <v>2011</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7295482295482295</v>
+        <v>0.7425216450216451</v>
       </c>
       <c r="G10" t="n">
-        <v>0.191291943192482</v>
+        <v>0.2052262276411057</v>
       </c>
       <c r="H10" t="n">
-        <v>0.542061984539032</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J10" t="n">
+        <v>0.1811923235654831</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7826086956521739</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1333333333333334</v>
+        <v>0.64</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.48</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2011</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7866666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8173015873015873</v>
+        <v>0.7812554112554112</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2524560212656212</v>
+        <v>0.2155699166949313</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6069641550507481</v>
+        <v>0.06405386481620562</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0.54444975619518</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1933333333333334</v>
+      <c r="W11" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1256,54 +1326,60 @@
         <v>2011</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6833333333333335</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5269047619047619</v>
+        <v>0.4994444444444445</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2902751847312317</v>
+        <v>0.2934111847312317</v>
       </c>
       <c r="H12" t="n">
+        <v>0.4208144796380091</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.4615384615384615</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.7</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.68</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.31</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.3066666666666666</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.3033333333333333</v>
       </c>
     </row>
@@ -1327,55 +1403,61 @@
         <v>2011</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7774908424908423</v>
+        <v>0.8428968253968253</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2702450270831586</v>
+        <v>0.1507788526946196</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02758309385041263</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0.4869203788268678</v>
       </c>
       <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>10</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.3333333333333333</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="S13" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1466666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1233333333333334</v>
+        <v>0.4899999999999999</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="14">
@@ -1398,55 +1480,61 @@
         <v>2012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.74</v>
+        <v>0.7533333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7462388387849418</v>
+        <v>0.7503796255344243</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2293773854275625</v>
+        <v>0.227927452314025</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5319497863256917</v>
+        <v>0.55057275498641</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0.5380971273781473</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="R14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T14" t="n">
         <v>0.76</v>
       </c>
-      <c r="S14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.28</v>
-      </c>
       <c r="U14" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1557,61 @@
         <v>2012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8803463203463203</v>
+        <v>0.8308333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1836292818407165</v>
+        <v>0.1903893359711869</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7331025587743101</v>
+        <v>0.54081673076076</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.6901332548249327</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="R15" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0.21</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="U15" t="n">
         <v>0.24</v>
       </c>
-      <c r="U15" t="n">
-        <v>0.27</v>
+      <c r="V15" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -1540,55 +1634,61 @@
         <v>2012</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8825735294117646</v>
+        <v>0.7975033738191633</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1964496672153473</v>
+        <v>0.213373526930809</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8360576629638672</v>
+        <v>0.1811923235654831</v>
       </c>
       <c r="I16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5565339326858521</v>
+      </c>
+      <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>13</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="P16" t="n">
         <v>0.8</v>
       </c>
-      <c r="N16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S16" t="n">
-        <v>0.18</v>
+        <v>0.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.32</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="17">
@@ -1611,55 +1711,61 @@
         <v>2012</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7400000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7653030303030303</v>
+        <v>0.7363003663003663</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2262333534232992</v>
+        <v>0.2567010621768958</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5572386412227298</v>
+        <v>0.54444975619518</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>0.6267763527465381</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0.5714285714285714</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>0.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="U17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
@@ -1682,54 +1788,60 @@
         <v>2012</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.6433333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5642857142857143</v>
+        <v>0.4844611528822055</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2805829703735584</v>
+        <v>0.2663622014903412</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4408602150537634</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="I18" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4861660079051383</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>11</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.22</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.1466666666666667</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.07333333333333333</v>
       </c>
     </row>
@@ -1753,55 +1865,61 @@
         <v>2012</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8969172932330828</v>
+        <v>0.8553968253968255</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2163941012571509</v>
+        <v>0.1915637961929806</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9992759537250263</v>
+        <v>0.4869203788268678</v>
       </c>
       <c r="I19" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.743917274901591</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="n">
         <v>7</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>15</v>
-      </c>
       <c r="M19" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="R19" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0.21</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="U19" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.2266666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -1824,56 +1942,32 @@
         <v>2011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7107156558275484</v>
+        <v>0.6793586070791954</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2509416835106334</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7479070647749126</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
+        <v>0.2422947484387324</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>13</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.3466666666666667</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.3733333333333334</v>
-      </c>
+        <v>0.2536687994291519</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1895,56 +1989,32 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.76</v>
+        <v>0.7766666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7174475524475523</v>
+        <v>0.7159173669467787</v>
       </c>
       <c r="G21" t="n">
-        <v>0.289332</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>7</v>
-      </c>
+        <v>0.290124</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.29</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1966,56 +2036,32 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.84</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8034373877756231</v>
+        <v>0.8140476190476191</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2935371696949005</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.01264334749430418</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
-      </c>
+        <v>0.3052151203155518</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.09333333333333334</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.04666666666666667</v>
-      </c>
+        <v>0.03066122904419899</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2037,56 +2083,32 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8262076760528773</v>
+        <v>0.8054960317460317</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1749310542796441</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.5177560433471168</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
+        <v>0.168529810590642</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>13</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.2833333333333333</v>
-      </c>
+        <v>0.5731696197915632</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2116,48 +2138,24 @@
       <c r="G24" t="n">
         <v>0.3442220598977356</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10</v>
-      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2179,56 +2177,32 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9246503496503496</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1890520927790247</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.09022014382267056</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
+        <v>0.1631188078049762</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>12</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.8695652173913043</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.1733462810478448</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2253,52 +2227,58 @@
         <v>0.8266666666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7821717171717172</v>
+        <v>0.7651037851037851</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1815465428449981</v>
+        <v>0.1728913535359017</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3953589496609311</v>
+        <v>0.2536687994291519</v>
       </c>
       <c r="I26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4456284258943104</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>12</v>
-      </c>
       <c r="M26" t="n">
-        <v>0.7619047619047619</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9133333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.9434782608695652</v>
       </c>
       <c r="G27" t="n">
-        <v>0.142092</v>
+        <v>0.152608</v>
       </c>
       <c r="H27" t="n">
-        <v>0.36</v>
+        <v>0.09</v>
       </c>
       <c r="I27" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K27" t="n">
         <v>9</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>12</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>15</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="P27" t="n">
         <v>0.9</v>
       </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S27" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="U27" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.31</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="28">
@@ -2395,52 +2381,58 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9373737373737373</v>
+        <v>0.95</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09886830300092697</v>
+        <v>0.07675102353096008</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6412296295166016</v>
+        <v>0.03066122904419899</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.5990811586380005</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>0.2</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R28" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.14</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T28" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.9466666666666668</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9047863247863247</v>
+        <v>0.9488235294117647</v>
       </c>
       <c r="G29" t="n">
-        <v>0.121324316674227</v>
+        <v>0.1063799079052805</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5505069190790638</v>
+        <v>0.5731696197915632</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.5319507003322614</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
         <v>15</v>
       </c>
-      <c r="M29" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O29" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S29" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
       <c r="U29" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5633333333333334</v>
+        <v>0.6966666666666668</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.6015384615384616</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3553442362180229</v>
+        <v>0.2769091049157587</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.754601226993865</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.8733333333333335</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9416666666666667</v>
+        <v>0.905952380952381</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06343412795935141</v>
+        <v>0.08119444656469808</v>
       </c>
       <c r="H31" t="n">
-        <v>0.790888611533765</v>
+        <v>0.1733462810478448</v>
       </c>
       <c r="I31" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.75047682599171</v>
+      </c>
+      <c r="K31" t="n">
         <v>9</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>15</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S31" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T31" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.76</v>
       </c>
       <c r="U31" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.17</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.1233333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2699,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.63</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="3">
@@ -2699,7 +2709,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2719,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2719,7 +2729,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.649</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="6">
@@ -2729,7 +2739,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="7">
@@ -2739,7 +2749,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.76</v>
+        <v>0.713</v>
       </c>
     </row>
   </sheetData>
@@ -2815,25 +2825,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.601</v>
       </c>
       <c r="D2" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="E2" t="n">
         <v>0.9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.492</v>
+        <v>0.487</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.667</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.213</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="3">
@@ -2848,25 +2858,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.747</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="G3" t="n">
-        <v>0.233</v>
+        <v>0.3</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>0.467</v>
       </c>
       <c r="I3" t="n">
-        <v>0.227</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="4">
@@ -2881,25 +2891,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.592</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>0.233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.267</v>
+        <v>0.578</v>
       </c>
       <c r="I4" t="n">
-        <v>0.293</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="5">
@@ -2914,25 +2924,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.669</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="F5" t="n">
-        <v>0.607</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="H5" t="n">
-        <v>0.422</v>
+        <v>0.867</v>
       </c>
       <c r="I5" t="n">
-        <v>0.218</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="6">
@@ -2947,25 +2957,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.702</v>
       </c>
       <c r="D6" t="n">
-        <v>0.721</v>
+        <v>0.613</v>
       </c>
       <c r="E6" t="n">
-        <v>0.867</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.472</v>
       </c>
       <c r="G6" t="n">
-        <v>0.133</v>
+        <v>0.067</v>
       </c>
       <c r="H6" t="n">
-        <v>0.422</v>
+        <v>0.778</v>
       </c>
       <c r="I6" t="n">
-        <v>0.191</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="7">
@@ -2980,25 +2990,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.73</v>
+        <v>0.545</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="F7" t="n">
-        <v>0.677</v>
+        <v>0.481</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="H7" t="n">
-        <v>0.267</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.213</v>
+        <v>0.333</v>
       </c>
     </row>
   </sheetData>
@@ -3044,7 +3054,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="3">
@@ -3054,7 +3064,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="4">
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3074,7 +3084,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="6">
@@ -3084,7 +3094,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="7">
@@ -3094,7 +3104,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="8">
@@ -3109,7 +3119,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="9">
@@ -3119,7 +3129,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.923</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10">
@@ -3129,7 +3139,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="11">
@@ -3139,7 +3149,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.867</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="12">
@@ -3149,7 +3159,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="13">
@@ -3159,7 +3169,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.887</v>
+        <v>0.903</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
+++ b/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -546,55 +556,61 @@
         <v>2010</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4449356199356199</v>
+        <v>0.519978354978355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3007399870535626</v>
+        <v>0.2998583294812446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4051125946677976</v>
+        <v>0.2231655884125293</v>
       </c>
       <c r="I2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.04049872052001606</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6086956521739131</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>0.5384615384615384</v>
       </c>
       <c r="P2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
       <c r="S2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.33</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -617,55 +633,61 @@
         <v>2010</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.45</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3610321704439352</v>
+        <v>0.3909486166007906</v>
       </c>
       <c r="G3" t="n">
-        <v>0.261028</v>
+        <v>0.259004</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T3" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -688,55 +710,61 @@
         <v>2010</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4540362905068787</v>
+        <v>0.4547552447552448</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3309194445610046</v>
+        <v>0.3249748647212982</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6843586564064026</v>
+        <v>0.009690718725323677</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6086956521739131</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -759,55 +787,61 @@
         <v>2010</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4266666666666667</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3646127565245212</v>
+        <v>0.3734640514284477</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3926556671239072</v>
+        <v>0.4058522375596354</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08150975529464062</v>
+        <v>0.2234067926243772</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J5" t="n">
-        <v>11</v>
+        <v>0.009387180199831516</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>0.45</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="R5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.29</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2266666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1633333333333333</v>
+        <v>0.51</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5066666666666667</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5033333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -839,46 +873,52 @@
         <v>0.3682919642501296</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.4208144796380091</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -901,55 +941,61 @@
         <v>2010</v>
       </c>
       <c r="E7" t="n">
-        <v>0.62</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5086363636363637</v>
+        <v>0.4906788380701425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3275847922554616</v>
+        <v>0.3586356286202021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7893669792601311</v>
+        <v>0.01672838630672052</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R7" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.29</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2933333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2966666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2011</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6723809523809523</v>
+        <v>0.6757142857142856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2295154823327183</v>
+        <v>0.2286170695507407</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5466160452390791</v>
+        <v>0.04049872052001606</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0.5469804229543777</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>0.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.29</v>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +1095,61 @@
         <v>2011</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6295921184079079</v>
+        <v>0.703971023816225</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2137274613314862</v>
+        <v>0.2139828872843262</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5138667912590348</v>
+        <v>0.25</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>0.5301995562666418</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O9" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R9" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.17</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1466666666666667</v>
+        <v>0.44</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1233333333333334</v>
+        <v>0.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +1172,61 @@
         <v>2011</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7295482295482295</v>
+        <v>0.7723909423909424</v>
       </c>
       <c r="G10" t="n">
-        <v>0.191291943192482</v>
+        <v>0.1740015149116516</v>
       </c>
       <c r="H10" t="n">
-        <v>0.542061984539032</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>0.1790300160646439</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7826086956521739</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.15</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1333333333333334</v>
+        <v>0.72</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.39</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.4266666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.4633333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2011</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7866666666666667</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8173015873015873</v>
+        <v>0.6635390559732665</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2524560212656212</v>
+        <v>0.2406275375564219</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6069641550507481</v>
+        <v>0.009387180199831516</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0.5665380815740352</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1933333333333334</v>
+      <c r="W11" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1256,54 +1326,60 @@
         <v>2011</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6833333333333335</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5269047619047619</v>
+        <v>0.4994444444444445</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2902751847312317</v>
+        <v>0.2979314347312317</v>
       </c>
       <c r="H12" t="n">
+        <v>0.4208144796380091</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.4615384615384615</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.7</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.68</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.31</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.3066666666666666</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.3033333333333333</v>
       </c>
     </row>
@@ -1327,55 +1403,61 @@
         <v>2011</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7774908424908423</v>
+        <v>0.8147209653092006</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2702450270831586</v>
+        <v>0.1500575637846308</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02758309385041263</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J13" t="n">
+        <v>0.3894227204390899</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>10</v>
-      </c>
       <c r="M13" t="n">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.625</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="R13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.76</v>
       </c>
-      <c r="S13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.1466666666666667</v>
-      </c>
       <c r="U13" t="n">
-        <v>0.1233333333333334</v>
+        <v>0.37</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4133333333333333</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.4566666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1398,55 +1480,61 @@
         <v>2012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.74</v>
+        <v>0.7533333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7462388387849418</v>
+        <v>0.7503796255344243</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2293773854275625</v>
+        <v>0.2271411060255309</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5319497863256917</v>
+        <v>0.5469804229543777</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J14" t="n">
+        <v>0.5398638525918656</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
         <v>12</v>
       </c>
-      <c r="M14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O14" t="n">
-        <v>0.7</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.2</v>
       </c>
-      <c r="R14" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.27</v>
-      </c>
       <c r="T14" t="n">
-        <v>0.28</v>
+        <v>0.72</v>
       </c>
       <c r="U14" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.3600000000000001</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3800000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1557,61 @@
         <v>2012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8803463203463203</v>
+        <v>0.8570833333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1836292818407165</v>
+        <v>0.1852884107624606</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7331025587743101</v>
+        <v>0.5301995562666418</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.6073013942111202</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R15" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0.21</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T15" t="n">
-        <v>0.24</v>
+        <v>0.76</v>
       </c>
       <c r="U15" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2133333333333334</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -1540,55 +1634,61 @@
         <v>2012</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8825735294117646</v>
+        <v>0.8260606060606061</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1964496672153473</v>
+        <v>0.2052984982728958</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8360576629638672</v>
+        <v>0.1790300160646439</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0.7093437314033508</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R16" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.18</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.22</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -1611,55 +1711,61 @@
         <v>2012</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7733333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7653030303030303</v>
+        <v>0.7643939393939394</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2262333534232992</v>
+        <v>0.2316837738679339</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5572386412227298</v>
+        <v>0.5665380815740352</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>0.5491067337270514</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6666666666666666</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="P17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S17" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.68</v>
       </c>
-      <c r="S17" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.24</v>
-      </c>
       <c r="U17" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.47</v>
       </c>
     </row>
     <row r="18">
@@ -1682,54 +1788,60 @@
         <v>2012</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.6433333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5642857142857143</v>
+        <v>0.4844611528822055</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2805829703735584</v>
+        <v>0.2663622014903412</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4408602150537634</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="I18" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4861660079051384</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>11</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.22</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.1466666666666667</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.07333333333333333</v>
       </c>
     </row>
@@ -1753,55 +1865,61 @@
         <v>2012</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8969172932330828</v>
+        <v>0.843560606060606</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2163941012571509</v>
+        <v>0.1936975925582458</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9992759537250263</v>
+        <v>0.3894227204390899</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.8028179757093012</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="R19" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="T19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W19" t="n">
         <v>0.24</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.27</v>
       </c>
     </row>
     <row r="20">
@@ -1824,56 +1942,32 @@
         <v>2011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7107156558275484</v>
+        <v>0.6793586070791954</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2509416835106334</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7479070647749126</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
+        <v>0.2422947484387324</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>13</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.3466666666666667</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.3733333333333334</v>
-      </c>
+        <v>0.2536687994291519</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1895,56 +1989,32 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.76</v>
+        <v>0.8366666666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7174475524475523</v>
+        <v>0.7575685425685426</v>
       </c>
       <c r="G21" t="n">
-        <v>0.289332</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>7</v>
-      </c>
+        <v>0.287216</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.29</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1966,56 +2036,32 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.84</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8034373877756231</v>
+        <v>0.8140476190476191</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2935371696949005</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.01264334749430418</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
-      </c>
+        <v>0.3052151203155518</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.09333333333333334</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.04666666666666667</v>
-      </c>
+        <v>0.03066122904419899</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2037,56 +2083,32 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8262076760528773</v>
+        <v>0.7919642857142856</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1749310542796441</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.5177560433471168</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
+        <v>0.1657546759866113</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>13</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.2833333333333333</v>
-      </c>
+        <v>0.4446888407804832</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2108,56 +2130,32 @@
         <v>2011</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5733333333333333</v>
+        <v>0.57</v>
       </c>
       <c r="F24" t="n">
-        <v>0.52</v>
+        <v>0.4866666666666667</v>
       </c>
       <c r="G24" t="n">
         <v>0.3442220598977356</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10</v>
-      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2179,56 +2177,32 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9246503496503496</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1890520927790247</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.09022014382267056</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
+        <v>0.1631188078049762</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>12</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.8695652173913043</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.1733462810478448</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2253,52 +2227,58 @@
         <v>0.8266666666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7821717171717172</v>
+        <v>0.7651037851037851</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1815465428449981</v>
+        <v>0.1728913535359017</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3953589496609311</v>
+        <v>0.2536687994291519</v>
       </c>
       <c r="I26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4456284258943104</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>12</v>
-      </c>
       <c r="M26" t="n">
-        <v>0.7619047619047619</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.9454545454545454</v>
       </c>
       <c r="G27" t="n">
-        <v>0.142092</v>
+        <v>0.150904</v>
       </c>
       <c r="H27" t="n">
-        <v>0.36</v>
+        <v>0.08</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="K27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" t="n">
+        <v>13</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>15</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.9473684210526315</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.1</v>
-      </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R27" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T27" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="U27" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -2395,52 +2381,58 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9373737373737373</v>
+        <v>0.95</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09886830300092697</v>
+        <v>0.07675102353096008</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6412296295166016</v>
+        <v>0.03066122904419899</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.5990811586380005</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>0.2</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R28" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.14</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T28" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9047863247863247</v>
+        <v>0.9318181818181818</v>
       </c>
       <c r="G29" t="n">
-        <v>0.121324316674227</v>
+        <v>0.1114075007321697</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5505069190790638</v>
+        <v>0.4446888407804832</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.5255866440639018</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L29" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8235294117647058</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7</v>
+        <v>13</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="R29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T29" t="n">
         <v>0.88</v>
       </c>
-      <c r="S29" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.24</v>
-      </c>
       <c r="U29" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.1066666666666667</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.1033333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5633333333333334</v>
+        <v>0.6966666666666668</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.6015384615384616</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3553442362180229</v>
+        <v>0.2769091049157587</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.754601226993865</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.8733333333333335</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9416666666666667</v>
+        <v>0.905952380952381</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06343412795935141</v>
+        <v>0.08119444656469808</v>
       </c>
       <c r="H31" t="n">
-        <v>0.790888611533765</v>
+        <v>0.1733462810478448</v>
       </c>
       <c r="I31" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.75047682599171</v>
+      </c>
+      <c r="K31" t="n">
         <v>9</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>15</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S31" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T31" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.76</v>
       </c>
       <c r="U31" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.17</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.1233333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2699,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.63</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="3">
@@ -2699,7 +2709,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.771</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2719,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2719,7 +2729,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.649</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="6">
@@ -2729,7 +2739,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="7">
@@ -2739,7 +2749,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.76</v>
+        <v>0.749</v>
       </c>
     </row>
   </sheetData>
@@ -2815,25 +2825,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.601</v>
       </c>
       <c r="D2" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="E2" t="n">
         <v>0.9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.492</v>
+        <v>0.487</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.667</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.213</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="3">
@@ -2848,25 +2858,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.762</v>
       </c>
       <c r="D3" t="n">
-        <v>0.747</v>
+        <v>0.602</v>
       </c>
       <c r="E3" t="n">
         <v>0.767</v>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>0.574</v>
       </c>
       <c r="G3" t="n">
         <v>0.233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>0.533</v>
       </c>
       <c r="I3" t="n">
-        <v>0.227</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="4">
@@ -2881,25 +2891,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.501</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>0.233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.267</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.293</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="5">
@@ -2914,25 +2924,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.622</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.521</v>
       </c>
       <c r="E5" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.607</v>
+        <v>0.47</v>
       </c>
       <c r="G5" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="H5" t="n">
-        <v>0.422</v>
+        <v>0.578</v>
       </c>
       <c r="I5" t="n">
-        <v>0.218</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="6">
@@ -2947,25 +2957,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="D6" t="n">
-        <v>0.721</v>
+        <v>0.629</v>
       </c>
       <c r="E6" t="n">
-        <v>0.867</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.494</v>
       </c>
       <c r="G6" t="n">
-        <v>0.133</v>
+        <v>0.067</v>
       </c>
       <c r="H6" t="n">
-        <v>0.422</v>
+        <v>0.733</v>
       </c>
       <c r="I6" t="n">
-        <v>0.191</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -2980,25 +2990,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.749</v>
       </c>
       <c r="D7" t="n">
-        <v>0.73</v>
+        <v>0.602</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.677</v>
+        <v>0.53</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="H7" t="n">
-        <v>0.267</v>
+        <v>0.622</v>
       </c>
       <c r="I7" t="n">
-        <v>0.213</v>
+        <v>0.258</v>
       </c>
     </row>
   </sheetData>
@@ -3044,7 +3054,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="3">
@@ -3054,7 +3064,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="4">
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3074,7 +3084,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="6">
@@ -3084,7 +3094,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="7">
@@ -3094,7 +3104,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="8">
@@ -3109,7 +3119,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="9">
@@ -3119,7 +3129,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.923</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10">
@@ -3129,7 +3139,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="11">
@@ -3139,7 +3149,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.867</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="12">
@@ -3149,7 +3159,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="13">
@@ -3159,7 +3169,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.887</v>
+        <v>0.903</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
+++ b/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -546,55 +556,61 @@
         <v>2010</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4449356199356199</v>
+        <v>0.519978354978355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3007399870535626</v>
+        <v>0.2998583294812446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4051125946677976</v>
+        <v>0.2231655884125293</v>
       </c>
       <c r="I2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.04049872052001606</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6086956521739131</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>0.5384615384615384</v>
       </c>
       <c r="P2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
       <c r="S2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.33</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -617,54 +633,60 @@
         <v>2010</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4966666666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3610321704439352</v>
+        <v>0.3992661578187894</v>
       </c>
       <c r="G3" t="n">
-        <v>0.261028</v>
+        <v>0.251244</v>
       </c>
       <c r="H3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.23</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>14</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.5882352941176471</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.44</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.28</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.1866666666666667</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.09333333333333334</v>
       </c>
     </row>
@@ -688,55 +710,61 @@
         <v>2010</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4540362905068787</v>
+        <v>0.4547552447552448</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3309194445610046</v>
+        <v>0.3249748647212982</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6843586564064026</v>
+        <v>0.009690718725323677</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6086956521739131</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -759,55 +787,61 @@
         <v>2010</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4266666666666667</v>
+        <v>0.4266666666666666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3646127565245212</v>
+        <v>0.3648755411255411</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3926556671239072</v>
+        <v>0.4163548777869769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08150975529464062</v>
+        <v>0.1675976620982564</v>
       </c>
       <c r="I5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.007483121794863587</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
       <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.6</v>
       </c>
-      <c r="N5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V5" t="n">
         <v>0.52</v>
       </c>
-      <c r="S5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.2266666666666667</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1633333333333333</v>
+      <c r="W5" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="6">
@@ -839,46 +873,52 @@
         <v>0.3682919642501296</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.4208144796380091</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -901,55 +941,61 @@
         <v>2010</v>
       </c>
       <c r="E7" t="n">
-        <v>0.62</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5086363636363637</v>
+        <v>0.4906788380701425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3275847922554616</v>
+        <v>0.3586356286202021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7893669792601311</v>
+        <v>0.01672838630672052</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R7" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.29</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2933333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2966666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2011</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6723809523809523</v>
+        <v>0.6757142857142856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2295154823327183</v>
+        <v>0.2262129513407036</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5466160452390791</v>
+        <v>0.04049872052001606</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0.5509219928636437</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>0.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.29</v>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +1095,61 @@
         <v>2011</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6295921184079079</v>
+        <v>0.6678588516746412</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2137274613314862</v>
+        <v>0.2094635123004371</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5138667912590348</v>
+        <v>0.23</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>0.5262242210666918</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O9" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R9" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.17</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1466666666666667</v>
+        <v>0.44</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1233333333333334</v>
+        <v>0.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +1172,61 @@
         <v>2011</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7295482295482295</v>
+        <v>0.7964457712909726</v>
       </c>
       <c r="G10" t="n">
-        <v>0.191291943192482</v>
+        <v>0.1834727078676224</v>
       </c>
       <c r="H10" t="n">
-        <v>0.542061984539032</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J10" t="n">
+        <v>0.3690356314182281</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7826086956521739</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0.15</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1333333333333334</v>
+        <v>0.68</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.46</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.5066666666666666</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.5533333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2011</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7866666666666667</v>
+        <v>0.66</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8173015873015873</v>
+        <v>0.5845682819595862</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2524560212656212</v>
+        <v>0.2319896577324677</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6069641550507481</v>
+        <v>0.007483121794863587</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0.3681064781613457</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1933333333333334</v>
+      <c r="W11" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1256,54 +1326,60 @@
         <v>2011</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6833333333333335</v>
+        <v>0.68</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5269047619047619</v>
+        <v>0.5224603174603174</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2902751847312317</v>
+        <v>0.2968714022812587</v>
       </c>
       <c r="H12" t="n">
+        <v>0.4208144796380091</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.4615384615384615</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.7</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.68</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.31</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.3066666666666666</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.3033333333333333</v>
       </c>
     </row>
@@ -1327,55 +1403,61 @@
         <v>2011</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7774908424908423</v>
+        <v>0.8533333333333332</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2702450270831586</v>
+        <v>0.1642185265571144</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02758309385041263</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0.117413863009697</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>13</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0.75</v>
       </c>
-      <c r="N13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.3333333333333333</v>
-      </c>
       <c r="R13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.76</v>
       </c>
-      <c r="S13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.1466666666666667</v>
-      </c>
       <c r="U13" t="n">
-        <v>0.1233333333333334</v>
+        <v>0.32</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="14">
@@ -1398,55 +1480,61 @@
         <v>2012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.74</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7462388387849418</v>
+        <v>0.7253796255344241</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2293773854275625</v>
+        <v>0.2293185541225835</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5319497863256917</v>
+        <v>0.5509219928636437</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0.5350775597259522</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="R14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T14" t="n">
         <v>0.76</v>
       </c>
-      <c r="S14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.28</v>
-      </c>
       <c r="U14" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1557,61 @@
         <v>2012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8803463203463203</v>
+        <v>0.8268939393939393</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1836292818407165</v>
+        <v>0.1830568113628217</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7331025587743101</v>
+        <v>0.5262242210666918</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.702347456161825</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="R15" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0.21</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="U15" t="n">
         <v>0.24</v>
       </c>
-      <c r="U15" t="n">
-        <v>0.27</v>
+      <c r="V15" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -1540,55 +1634,61 @@
         <v>2012</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8825735294117646</v>
+        <v>0.8740079365079365</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1964496672153473</v>
+        <v>0.188811182975769</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8360576629638672</v>
+        <v>0.3690356314182281</v>
       </c>
       <c r="I16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7477943301200867</v>
+      </c>
+      <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>13</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="P16" t="n">
         <v>0.8</v>
       </c>
-      <c r="N16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S16" t="n">
-        <v>0.18</v>
+        <v>0.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.32</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="17">
@@ -1611,55 +1711,61 @@
         <v>2012</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7653030303030303</v>
+        <v>0.8398809523809524</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2262333534232992</v>
+        <v>0.2136895041241525</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5572386412227298</v>
+        <v>0.3681064781613457</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>0.5459909547953015</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S17" t="n">
         <v>0.8</v>
       </c>
-      <c r="O17" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.26</v>
-      </c>
       <c r="T17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="V17" t="n">
         <v>0.24</v>
       </c>
-      <c r="U17" t="n">
-        <v>0.22</v>
+      <c r="W17" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="18">
@@ -1682,54 +1788,60 @@
         <v>2012</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.6433333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5642857142857143</v>
+        <v>0.4844611528822055</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2805829703735584</v>
+        <v>0.2663622014903412</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4408602150537634</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="I18" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4861660079051384</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>11</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.22</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.1466666666666667</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.07333333333333333</v>
       </c>
     </row>
@@ -1753,56 +1865,62 @@
         <v>2012</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.88</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8969172932330828</v>
+        <v>0.8817857142857143</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2163941012571509</v>
+        <v>0.1984457761715843</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9992759537250263</v>
+        <v>0.117413863009697</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.8970361081168594</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8235294117647058</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="R19" t="n">
-        <v>0.88</v>
+        <v>0.1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.21</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U19" t="n">
         <v>0.27</v>
       </c>
+      <c r="V19" t="n">
+        <v>0.2133333333333333</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.1566666666666667</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1824,56 +1942,32 @@
         <v>2011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7107156558275484</v>
+        <v>0.6793586070791954</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2509416835106334</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7479070647749126</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
+        <v>0.2422947484387324</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>13</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.3466666666666667</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.3733333333333334</v>
-      </c>
+        <v>0.2536687994291519</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1895,56 +1989,32 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.76</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7174475524475523</v>
+        <v>0.8600135975135975</v>
       </c>
       <c r="G21" t="n">
-        <v>0.289332</v>
-      </c>
-      <c r="H21" t="n">
+        <v>0.281948</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
         <v>0.1</v>
       </c>
-      <c r="I21" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.29</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1966,56 +2036,32 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.84</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8034373877756231</v>
+        <v>0.8140476190476191</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2935371696949005</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.01264334749430418</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
-      </c>
+        <v>0.3052151203155518</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.09333333333333334</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.04666666666666667</v>
-      </c>
+        <v>0.03066122904419899</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2037,56 +2083,32 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8262076760528773</v>
+        <v>0.8112640056022409</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1749310542796441</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.5177560433471168</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
+        <v>0.1792945945019521</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>13</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.2833333333333333</v>
-      </c>
+        <v>0.2104223693673257</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2108,56 +2130,32 @@
         <v>2011</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5733333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>0.52</v>
+        <v>0.4700000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3442220598977356</v>
-      </c>
-      <c r="H24" t="n">
+        <v>0.3655222790357926</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2179,56 +2177,32 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9246503496503496</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1890520927790247</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.09022014382267056</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
+        <v>0.1631188078049762</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>12</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.8695652173913043</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.1733462810478448</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2253,52 +2227,58 @@
         <v>0.8266666666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7821717171717172</v>
+        <v>0.7651037851037851</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1815465428449981</v>
+        <v>0.1728913535359017</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3953589496609311</v>
+        <v>0.2536687994291519</v>
       </c>
       <c r="I26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4456284258943104</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>12</v>
-      </c>
       <c r="M26" t="n">
-        <v>0.7619047619047619</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.9454545454545454</v>
       </c>
       <c r="G27" t="n">
-        <v>0.142092</v>
+        <v>0.137496</v>
       </c>
       <c r="H27" t="n">
-        <v>0.36</v>
+        <v>0.1</v>
       </c>
       <c r="I27" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K27" t="n">
         <v>9</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>11</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>15</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P27" t="n">
         <v>0.9</v>
       </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S27" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="U27" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.1633333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -2395,52 +2381,58 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9373737373737373</v>
+        <v>0.95</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09886830300092697</v>
+        <v>0.07675102353096008</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6412296295166016</v>
+        <v>0.03066122904419899</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J28" t="n">
+        <v>0.5990811586380005</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11</v>
+      </c>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>15</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.8888888888888888</v>
-      </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>0.2</v>
-      </c>
       <c r="Q28" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="R28" t="n">
-        <v>0.92</v>
-      </c>
       <c r="S28" t="n">
-        <v>0.14</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T28" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.9266666666666667</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9047863247863247</v>
+        <v>0.9170306001188354</v>
       </c>
       <c r="G29" t="n">
-        <v>0.121324316674227</v>
+        <v>0.1193665283871371</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5505069190790638</v>
+        <v>0.2104223693673257</v>
       </c>
       <c r="I29" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4958754183688527</v>
+      </c>
+      <c r="K29" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" t="n">
         <v>7</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>15</v>
-      </c>
       <c r="M29" t="n">
-        <v>0.8235294117647058</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="R29" t="n">
-        <v>0.88</v>
+        <v>0.1</v>
       </c>
       <c r="S29" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="U29" t="n">
         <v>0.21</v>
       </c>
-      <c r="T29" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.27</v>
+      <c r="V29" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.1366666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5633333333333334</v>
+        <v>0.6966666666666668</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.6015384615384616</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3553442362180229</v>
+        <v>0.2769091049157587</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.754601226993865</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.8733333333333335</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9416666666666667</v>
+        <v>0.905952380952381</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06343412795935141</v>
+        <v>0.08119444656469808</v>
       </c>
       <c r="H31" t="n">
-        <v>0.790888611533765</v>
+        <v>0.1733462810478448</v>
       </c>
       <c r="I31" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.75047682599171</v>
+      </c>
+      <c r="K31" t="n">
         <v>9</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>15</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S31" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T31" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.76</v>
       </c>
       <c r="U31" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.17</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.1233333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2699,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.63</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="3">
@@ -2699,7 +2709,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.771</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2719,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="5">
@@ -2719,7 +2729,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.649</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="6">
@@ -2729,7 +2739,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="7">
@@ -2739,7 +2749,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.76</v>
+        <v>0.749</v>
       </c>
     </row>
   </sheetData>
@@ -2815,25 +2825,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.606</v>
       </c>
       <c r="D2" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="E2" t="n">
         <v>0.9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.492</v>
+        <v>0.487</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.667</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.213</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="3">
@@ -2848,25 +2858,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.787</v>
       </c>
       <c r="D3" t="n">
-        <v>0.747</v>
+        <v>0.625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>0.547</v>
       </c>
       <c r="G3" t="n">
-        <v>0.233</v>
+        <v>0.167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>0.578</v>
       </c>
       <c r="I3" t="n">
-        <v>0.227</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="4">
@@ -2881,25 +2891,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.592</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>0.233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.267</v>
+        <v>0.578</v>
       </c>
       <c r="I4" t="n">
-        <v>0.293</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="5">
@@ -2914,25 +2924,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.631</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.523</v>
       </c>
       <c r="E5" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.607</v>
+        <v>0.395</v>
       </c>
       <c r="G5" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.422</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.218</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="6">
@@ -2947,25 +2957,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="D6" t="n">
-        <v>0.721</v>
+        <v>0.624</v>
       </c>
       <c r="E6" t="n">
-        <v>0.867</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.483</v>
       </c>
       <c r="G6" t="n">
-        <v>0.133</v>
+        <v>0.067</v>
       </c>
       <c r="H6" t="n">
-        <v>0.422</v>
+        <v>0.733</v>
       </c>
       <c r="I6" t="n">
-        <v>0.191</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -2980,25 +2990,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.749</v>
       </c>
       <c r="D7" t="n">
-        <v>0.73</v>
+        <v>0.555</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="F7" t="n">
-        <v>0.677</v>
+        <v>0.512</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="H7" t="n">
-        <v>0.267</v>
+        <v>0.578</v>
       </c>
       <c r="I7" t="n">
-        <v>0.213</v>
+        <v>0.329</v>
       </c>
     </row>
   </sheetData>
@@ -3044,7 +3054,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="3">
@@ -3054,7 +3064,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="4">
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="5">
@@ -3074,7 +3084,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="6">
@@ -3084,7 +3094,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="7">
@@ -3094,7 +3104,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="8">
@@ -3109,7 +3119,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="9">
@@ -3119,7 +3129,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.923</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10">
@@ -3129,7 +3139,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="11">
@@ -3139,7 +3149,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.867</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="12">
@@ -3149,7 +3159,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="13">
@@ -3159,7 +3169,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.887</v>
+        <v>0.903</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
+++ b/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -546,55 +556,61 @@
         <v>2010</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4449356199356199</v>
+        <v>0.519978354978355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3007399870535626</v>
+        <v>0.2998583294812446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4051125946677976</v>
+        <v>0.2231655884125293</v>
       </c>
       <c r="I2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.04049872052001606</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6086956521739131</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>0.5384615384615384</v>
       </c>
       <c r="P2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
       <c r="S2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.33</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -617,54 +633,60 @@
         <v>2010</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.5233333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3610321704439352</v>
+        <v>0.4018357592699698</v>
       </c>
       <c r="G3" t="n">
-        <v>0.261028</v>
+        <v>0.247848</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="I3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>14</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.5882352941176471</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.44</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.28</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.1866666666666667</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.09333333333333334</v>
       </c>
     </row>
@@ -688,55 +710,61 @@
         <v>2010</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4540362905068787</v>
+        <v>0.4547552447552448</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3309194445610046</v>
+        <v>0.3249748647212982</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6843586564064026</v>
+        <v>0.009690718725323677</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6086956521739131</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -759,55 +787,61 @@
         <v>2010</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4266666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3646127565245212</v>
+        <v>0.3913767819727572</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3926556671239072</v>
+        <v>0.4084965984348273</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08150975529464062</v>
+        <v>0.01301643857352878</v>
       </c>
       <c r="I5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.04294901516253519</v>
+      </c>
+      <c r="K5" t="n">
         <v>9</v>
       </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.6</v>
-      </c>
       <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="P5" t="n">
         <v>0.9</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.52</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.29</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2266666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1633333333333333</v>
+        <v>0.35</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1833333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -836,49 +870,55 @@
         <v>0.4027272727272728</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3682919642501296</v>
+        <v>0.3682919642501295</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4208144796380091</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.420814479638009</v>
+      </c>
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -901,55 +941,61 @@
         <v>2010</v>
       </c>
       <c r="E7" t="n">
-        <v>0.62</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5086363636363637</v>
+        <v>0.4906788380701425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3275847922554616</v>
+        <v>0.3586356286202021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7893669792601311</v>
+        <v>0.01672838630672052</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R7" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.29</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2933333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2966666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2011</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6723809523809523</v>
+        <v>0.6757142857142856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2295154823327183</v>
+        <v>0.2257781571759269</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5466160452390791</v>
+        <v>0.04049872052001606</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0.5516014851980061</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>0.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.29</v>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +1095,61 @@
         <v>2011</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6295921184079079</v>
+        <v>0.5960839598997494</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2137274613314862</v>
+        <v>0.219036064767026</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5138667912590348</v>
+        <v>0.26</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>0.4717034559157639</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O9" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R9" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.17</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1466666666666667</v>
+        <v>0.44</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1233333333333334</v>
+        <v>0.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1117,52 +1175,58 @@
         <v>0.8266666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7295482295482295</v>
+        <v>0.7699062049062049</v>
       </c>
       <c r="G10" t="n">
-        <v>0.191291943192482</v>
+        <v>0.1659564226865768</v>
       </c>
       <c r="H10" t="n">
-        <v>0.542061984539032</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J10" t="n">
+        <v>0.3086777031421661</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.7826086956521739</v>
-      </c>
       <c r="N10" t="n">
-        <v>0.9</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0.15</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1333333333333334</v>
+        <v>0.76</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2011</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7866666666666667</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8173015873015873</v>
+        <v>0.490301876486087</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2524560212656212</v>
+        <v>0.2459081482269538</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6069641550507481</v>
+        <v>0.04294901516253519</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0.3846631296840507</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1933333333333334</v>
+      <c r="W11" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1256,54 +1326,60 @@
         <v>2011</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6833333333333335</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5269047619047619</v>
+        <v>0.4994444444444445</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2902751847312317</v>
+        <v>0.2934111847312317</v>
       </c>
       <c r="H12" t="n">
+        <v>0.420814479638009</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.4615384615384615</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.7</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.68</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.31</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.3066666666666666</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.3033333333333333</v>
       </c>
     </row>
@@ -1327,55 +1403,61 @@
         <v>2011</v>
       </c>
       <c r="E13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8405691530691531</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1448888339515129</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7182909777301603</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2687835546923359</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0.8</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.7774908424908423</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.2702450270831586</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.02758309385041263</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>10</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.3333333333333333</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
       <c r="S13" t="n">
-        <v>0.17</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1466666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1233333333333334</v>
+        <v>0.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4933333333333333</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5466666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1398,55 +1480,61 @@
         <v>2012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.74</v>
+        <v>0.7533333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7462388387849418</v>
+        <v>0.7503796255344243</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2293773854275625</v>
+        <v>0.2269692551191244</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5319497863256917</v>
+        <v>0.5516014851980061</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0.5402561152358011</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="R14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T14" t="n">
         <v>0.76</v>
       </c>
-      <c r="S14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.28</v>
-      </c>
       <c r="U14" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1557,61 @@
         <v>2012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8866666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8803463203463203</v>
+        <v>0.8683658008658007</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1836292818407165</v>
+        <v>0.1738105834797435</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7331025587743101</v>
+        <v>0.4717034559157639</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.657526235344746</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8235294117647058</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0.88</v>
+        <v>0.1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="U15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="16">
@@ -1540,55 +1634,61 @@
         <v>2012</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8825735294117646</v>
+        <v>0.8517857142857143</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1964496672153473</v>
+        <v>0.1835115253925323</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8360576629638672</v>
+        <v>0.3086777031421661</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0.7408987283706665</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="R16" t="n">
-        <v>0.84</v>
+        <v>0.1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.18</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2133333333333333</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1566666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -1611,55 +1711,61 @@
         <v>2012</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7653030303030303</v>
+        <v>0.6315747702589808</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2262333534232992</v>
+        <v>0.2411265542170853</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5572386412227298</v>
+        <v>0.3846631296840507</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>0.4748888626187611</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R17" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.26</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T17" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="U17" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="18">
@@ -1682,54 +1788,60 @@
         <v>2012</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5642857142857143</v>
+        <v>0.5144611528822054</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2805829703735584</v>
+        <v>0.2713278107498441</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4408602150537634</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="I18" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>11</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.22</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.1466666666666667</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.07333333333333333</v>
       </c>
     </row>
@@ -1753,55 +1865,61 @@
         <v>2012</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8733333333333334</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8969172932330828</v>
+        <v>0.8855727554179568</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2163941012571509</v>
+        <v>0.2052292745394733</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9992759537250263</v>
+        <v>0.2687835546923359</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.8954311436183544</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8235294117647058</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0.88</v>
+        <v>0.1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="20">
@@ -1824,56 +1942,32 @@
         <v>2011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7107156558275484</v>
+        <v>0.6793586070791954</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2509416835106334</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7479070647749126</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
+        <v>0.2422947484387324</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>13</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.3466666666666667</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.3733333333333334</v>
-      </c>
+        <v>0.2536687994291519</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1895,56 +1989,32 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.76</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7174475524475523</v>
+        <v>0.7812745098039217</v>
       </c>
       <c r="G21" t="n">
-        <v>0.289332</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>7</v>
-      </c>
+        <v>0.270492</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.29</v>
-      </c>
+        <v>0.13</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1966,56 +2036,32 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.84</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8034373877756231</v>
+        <v>0.8140476190476191</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2935371696949005</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.01264334749430418</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
-      </c>
+        <v>0.3052151203155518</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.09333333333333334</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.04666666666666667</v>
-      </c>
+        <v>0.03066122904419899</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2037,56 +2083,32 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8262076760528773</v>
+        <v>0.7623856209150327</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1749310542796441</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.5177560433471168</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
+        <v>0.183363815636871</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>13</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.2833333333333333</v>
-      </c>
+        <v>0.5543724247582746</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2108,56 +2130,32 @@
         <v>2011</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5733333333333333</v>
+        <v>0.54</v>
       </c>
       <c r="F24" t="n">
-        <v>0.52</v>
+        <v>0.4700000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3442220598977356</v>
-      </c>
-      <c r="H24" t="n">
+        <v>0.3656574872564524</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2179,56 +2177,32 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9246503496503496</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1890520927790247</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.09022014382267056</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
+        <v>0.1631188078049762</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>12</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.8695652173913043</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.1733462810478448</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2253,52 +2227,58 @@
         <v>0.8266666666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7821717171717172</v>
+        <v>0.7651037851037851</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1815465428449981</v>
+        <v>0.1728913535359017</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3953589496609311</v>
+        <v>0.2536687994291519</v>
       </c>
       <c r="I26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4456284258943104</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>12</v>
-      </c>
       <c r="M26" t="n">
-        <v>0.7619047619047619</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.9476190476190476</v>
       </c>
       <c r="G27" t="n">
-        <v>0.142092</v>
+        <v>0.140248</v>
       </c>
       <c r="H27" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="I27" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K27" t="n">
         <v>9</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>9</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>15</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N27" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="P27" t="n">
         <v>0.9</v>
       </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S27" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="T27" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.6</v>
       </c>
       <c r="U27" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="28">
@@ -2395,52 +2381,58 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9373737373737373</v>
+        <v>0.95</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09886830300092697</v>
+        <v>0.07675102353096008</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6412296295166016</v>
+        <v>0.03066122904419899</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J28" t="n">
+        <v>0.5990811586380005</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11</v>
+      </c>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>15</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.8888888888888888</v>
-      </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>0.2</v>
-      </c>
       <c r="Q28" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="R28" t="n">
-        <v>0.92</v>
-      </c>
       <c r="S28" t="n">
-        <v>0.14</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T28" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9047863247863247</v>
+        <v>0.9318181818181818</v>
       </c>
       <c r="G29" t="n">
-        <v>0.121324316674227</v>
+        <v>0.1081368510327895</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5505069190790638</v>
+        <v>0.5543724247582746</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J29" t="n">
+        <v>0.5579803944189268</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
         <v>15</v>
       </c>
-      <c r="M29" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O29" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S29" t="n">
         <v>0</v>
       </c>
-      <c r="R29" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.21</v>
-      </c>
       <c r="T29" t="n">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
       <c r="U29" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5633333333333334</v>
+        <v>0.6966666666666668</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.6015384615384616</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3553442362180229</v>
+        <v>0.2769091049157587</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.754601226993865</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.8733333333333335</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9416666666666667</v>
+        <v>0.905952380952381</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06343412795935141</v>
+        <v>0.08119444656469808</v>
       </c>
       <c r="H31" t="n">
-        <v>0.790888611533765</v>
+        <v>0.1733462810478448</v>
       </c>
       <c r="I31" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.75047682599171</v>
+      </c>
+      <c r="K31" t="n">
         <v>9</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>15</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S31" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T31" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.76</v>
       </c>
       <c r="U31" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.17</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.1233333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2699,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.63</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="3">
@@ -2699,7 +2709,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.771</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2719,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2719,7 +2729,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.649</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="6">
@@ -2729,7 +2739,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="7">
@@ -2739,7 +2749,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.76</v>
+        <v>0.744</v>
       </c>
     </row>
   </sheetData>
@@ -2815,25 +2825,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.604</v>
       </c>
       <c r="D2" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="E2" t="n">
         <v>0.9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.492</v>
+        <v>0.487</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.667</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.213</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="3">
@@ -2848,25 +2858,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.784</v>
       </c>
       <c r="D3" t="n">
-        <v>0.747</v>
+        <v>0.588</v>
       </c>
       <c r="E3" t="n">
         <v>0.767</v>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>0.572</v>
       </c>
       <c r="G3" t="n">
         <v>0.233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>0.533</v>
       </c>
       <c r="I3" t="n">
-        <v>0.227</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="4">
@@ -2881,25 +2891,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.592</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>0.233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.267</v>
+        <v>0.578</v>
       </c>
       <c r="I4" t="n">
-        <v>0.293</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="5">
@@ -2914,22 +2924,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.833</v>
+        <v>0.967</v>
       </c>
       <c r="F5" t="n">
-        <v>0.607</v>
+        <v>0.403</v>
       </c>
       <c r="G5" t="n">
-        <v>0.167</v>
+        <v>0.033</v>
       </c>
       <c r="H5" t="n">
-        <v>0.422</v>
+        <v>0.956</v>
       </c>
       <c r="I5" t="n">
         <v>0.218</v>
@@ -2947,22 +2957,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.712</v>
       </c>
       <c r="D6" t="n">
-        <v>0.721</v>
+        <v>0.606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.867</v>
+        <v>0.967</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.444</v>
       </c>
       <c r="G6" t="n">
-        <v>0.133</v>
+        <v>0.033</v>
       </c>
       <c r="H6" t="n">
-        <v>0.422</v>
+        <v>0.822</v>
       </c>
       <c r="I6" t="n">
         <v>0.191</v>
@@ -2980,25 +2990,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.744</v>
       </c>
       <c r="D7" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.677</v>
+        <v>0.541</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="H7" t="n">
-        <v>0.267</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.213</v>
+        <v>0.253</v>
       </c>
     </row>
   </sheetData>
@@ -3044,7 +3054,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="3">
@@ -3054,7 +3064,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="4">
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3074,7 +3084,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="6">
@@ -3084,7 +3094,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="7">
@@ -3094,7 +3104,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="8">
@@ -3109,7 +3119,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="9">
@@ -3119,7 +3129,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.923</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10">
@@ -3129,7 +3139,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="11">
@@ -3139,7 +3149,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.867</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="12">
@@ -3149,7 +3159,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="13">
@@ -3159,7 +3169,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.887</v>
+        <v>0.903</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
+++ b/outputs/results/12b_gran/results_12b_isolate_gran_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -546,55 +556,61 @@
         <v>2010</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4449356199356199</v>
+        <v>0.519978354978355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3007399870535626</v>
+        <v>0.2998583294812446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4051125946677976</v>
+        <v>0.2231655884125293</v>
       </c>
       <c r="I2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.04049872052001606</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6086956521739131</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>0.5384615384615384</v>
       </c>
       <c r="P2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
       <c r="S2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.33</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -617,55 +633,61 @@
         <v>2010</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3610321704439352</v>
+        <v>0.4103209109730849</v>
       </c>
       <c r="G3" t="n">
-        <v>0.261028</v>
+        <v>0.250856</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="I3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T3" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -688,55 +710,61 @@
         <v>2010</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4540362905068787</v>
+        <v>0.4547552447552448</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3309194445610046</v>
+        <v>0.3249748647212982</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6843586564064026</v>
+        <v>0.009690718725323677</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6086956521739131</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -759,55 +787,61 @@
         <v>2010</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4266666666666667</v>
+        <v>0.4533333333333334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3646127565245212</v>
+        <v>0.3748485797827903</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3926556671239072</v>
+        <v>0.413228283967897</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08150975529464062</v>
+        <v>0.0667044604265609</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J5" t="n">
-        <v>11</v>
+        <v>0.05581207567218907</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>0.45</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T5" t="n">
         <v>0.52</v>
       </c>
-      <c r="S5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.2266666666666667</v>
-      </c>
       <c r="U5" t="n">
-        <v>0.1633333333333333</v>
+        <v>0.34</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.2466666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -839,46 +873,52 @@
         <v>0.3682919642501296</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.4208144796380091</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -901,55 +941,61 @@
         <v>2010</v>
       </c>
       <c r="E7" t="n">
-        <v>0.62</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5086363636363637</v>
+        <v>0.4906788380701425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3275847922554616</v>
+        <v>0.3586356286202021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7893669792601311</v>
+        <v>0.01672838630672052</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R7" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.29</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2933333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2966666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2011</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6723809523809523</v>
+        <v>0.6757142857142856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2295154823327183</v>
+        <v>0.2285666340427561</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5466160452390791</v>
+        <v>0.04049872052001606</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0.5470663661436941</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>0.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.29</v>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +1095,61 @@
         <v>2011</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6295921184079079</v>
+        <v>0.6280405623787977</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2137274613314862</v>
+        <v>0.2167722727540856</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5138667912590348</v>
+        <v>0.18</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>0.4988983093945373</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.1466666666666667</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1233333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +1172,61 @@
         <v>2011</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.7866666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7295482295482295</v>
+        <v>0.7303526538820656</v>
       </c>
       <c r="G10" t="n">
-        <v>0.191291943192482</v>
+        <v>0.1922027766704559</v>
       </c>
       <c r="H10" t="n">
-        <v>0.542061984539032</v>
+        <v>0.5276885628700256</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J10" t="n">
+        <v>0.3598323166370392</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.7826086956521739</v>
-      </c>
       <c r="N10" t="n">
-        <v>0.9</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0.15</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1333333333333334</v>
+        <v>0.76</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2011</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7866666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8173015873015873</v>
+        <v>0.6359905445431761</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2524560212656212</v>
+        <v>0.2591950333957129</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6069641550507481</v>
+        <v>0.05581207567218907</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0.645703656766815</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1933333333333334</v>
+      <c r="W11" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1256,55 +1326,61 @@
         <v>2011</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6833333333333335</v>
+        <v>0.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5269047619047619</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2902751847312317</v>
+        <v>0.380736</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.4208144796380091</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
       <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S12" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.31</v>
-      </c>
       <c r="T12" t="n">
-        <v>0.3066666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3033333333333333</v>
+        <v>0.45</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -1327,55 +1403,61 @@
         <v>2011</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7774908424908423</v>
+        <v>0.7250463343845697</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2702450270831586</v>
+        <v>0.241594111130385</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02758309385041263</v>
+        <v>0.7182909777301603</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0.1928659448538993</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9</v>
+        <v>12</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="R13" t="n">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
       <c r="S13" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1466666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1233333333333334</v>
+        <v>0.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1398,55 +1480,61 @@
         <v>2012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.74</v>
+        <v>0.7533333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7462388387849418</v>
+        <v>0.7503796255344243</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2293773854275625</v>
+        <v>0.2278116986491379</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5319497863256917</v>
+        <v>0.5470663661436941</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0.5383543658583445</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="R14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T14" t="n">
         <v>0.76</v>
       </c>
-      <c r="S14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.28</v>
-      </c>
       <c r="U14" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1557,61 @@
         <v>2012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8733333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8803463203463203</v>
+        <v>0.8876190476190476</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1836292818407165</v>
+        <v>0.1743222837780199</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7331025587743101</v>
+        <v>0.4988983093945373</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7427685951429934</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R15" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0.21</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T15" t="n">
-        <v>0.24</v>
+        <v>0.76</v>
       </c>
       <c r="U15" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2133333333333334</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -1540,55 +1634,61 @@
         <v>2012</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8825735294117646</v>
+        <v>0.8532323232323232</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1964496672153473</v>
+        <v>0.1939588487148285</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8360576629638672</v>
+        <v>0.3598323166370392</v>
       </c>
       <c r="I16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7526405453681946</v>
+      </c>
+      <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>13</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="P16" t="n">
         <v>0.8</v>
       </c>
-      <c r="N16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S16" t="n">
-        <v>0.18</v>
+        <v>0.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.32</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="17">
@@ -1611,55 +1711,61 @@
         <v>2012</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7653030303030303</v>
+        <v>0.7150757137599242</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2262333534232992</v>
+        <v>0.2421686935355879</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5572386412227298</v>
+        <v>0.645703656766815</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J17" t="n">
+        <v>0.6443064357794667</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>6</v>
       </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>9</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="N17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0.8</v>
       </c>
-      <c r="O17" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="S17" t="n">
-        <v>0.26</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T17" t="n">
-        <v>0.24</v>
+        <v>0.72</v>
       </c>
       <c r="U17" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4933333333333333</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.5466666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -1682,55 +1788,61 @@
         <v>2012</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5642857142857143</v>
+        <v>0.5144611528822054</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2805829703735584</v>
+        <v>0.2713278107498441</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4408602150537634</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
-        <v>11</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6451612903225806</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
-        <v>0.4761904761904762</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.22</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1466666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07333333333333333</v>
+        <v>0.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -1753,55 +1865,61 @@
         <v>2012</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8969172932330828</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2163941012571509</v>
+        <v>0.1792063404334944</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9992759537250263</v>
+        <v>0.1928659448538993</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.7660718772403965</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8235294117647058</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P19" t="n">
         <v>1</v>
       </c>
-      <c r="P19" t="n">
-        <v>0.3</v>
-      </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.21</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -1824,56 +1942,32 @@
         <v>2011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7107156558275484</v>
+        <v>0.6793586070791954</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2509416835106334</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7479070647749126</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
+        <v>0.2422947484387324</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>13</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.3466666666666667</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.3733333333333334</v>
-      </c>
+        <v>0.2536687994291519</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1895,56 +1989,32 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7174475524475523</v>
+        <v>0.8458241758241758</v>
       </c>
       <c r="G21" t="n">
-        <v>0.289332</v>
-      </c>
-      <c r="H21" t="n">
+        <v>0.266376</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
         <v>0.1</v>
       </c>
-      <c r="I21" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.29</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1966,56 +2036,32 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.84</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8034373877756231</v>
+        <v>0.8140476190476191</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2935371696949005</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.01264334749430418</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
-      </c>
+        <v>0.3052151203155518</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.09333333333333334</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.04666666666666667</v>
-      </c>
+        <v>0.03066122904419899</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2037,56 +2083,32 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8262076760528773</v>
+        <v>0.7934187370600414</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1749310542796441</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.5177560433471168</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
+        <v>0.1722405461679267</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>13</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.2833333333333333</v>
-      </c>
+        <v>0.5028222744215738</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2108,56 +2130,32 @@
         <v>2011</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5733333333333333</v>
+        <v>0.57</v>
       </c>
       <c r="F24" t="n">
-        <v>0.52</v>
+        <v>0.4866666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3442220598977356</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10</v>
-      </c>
+        <v>0.3443572681183953</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2179,56 +2177,32 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9246503496503496</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1890520927790247</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.09022014382267056</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
+        <v>0.1631188078049762</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>12</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.8695652173913043</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.1733462810478448</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2253,52 +2227,58 @@
         <v>0.8266666666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7821717171717172</v>
+        <v>0.7651037851037851</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1815465428449981</v>
+        <v>0.1728913535359017</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3953589496609311</v>
+        <v>0.2536687994291519</v>
       </c>
       <c r="I26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4456284258943104</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>12</v>
-      </c>
       <c r="M26" t="n">
-        <v>0.7619047619047619</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.9334782608695652</v>
       </c>
       <c r="G27" t="n">
-        <v>0.142092</v>
+        <v>0.16242</v>
       </c>
       <c r="H27" t="n">
-        <v>0.36</v>
+        <v>0.1</v>
       </c>
       <c r="I27" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K27" t="n">
         <v>9</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>12</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>15</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="P27" t="n">
         <v>0.9</v>
       </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S27" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="U27" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.31</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="28">
@@ -2395,52 +2381,58 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9373737373737373</v>
+        <v>0.95</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09886830300092697</v>
+        <v>0.07675102353096008</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6412296295166016</v>
+        <v>0.03066122904419899</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.5990811586380005</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>0.2</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R28" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.14</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T28" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9047863247863247</v>
+        <v>0.9376190476190477</v>
       </c>
       <c r="G29" t="n">
-        <v>0.121324316674227</v>
+        <v>0.1099154705022434</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5505069190790638</v>
+        <v>0.5028222744215738</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.5836471141114647</v>
       </c>
       <c r="K29" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" t="n">
         <v>3</v>
       </c>
-      <c r="L29" t="n">
-        <v>15</v>
-      </c>
       <c r="M29" t="n">
-        <v>0.8235294117647058</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7</v>
+        <v>12</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R29" t="n">
-        <v>0.88</v>
+        <v>0.1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24</v>
+        <v>0.84</v>
       </c>
       <c r="U29" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5633333333333334</v>
+        <v>0.6966666666666668</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.6015384615384616</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3553442362180229</v>
+        <v>0.2769091049157587</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.754601226993865</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.8733333333333335</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9416666666666667</v>
+        <v>0.905952380952381</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06343412795935141</v>
+        <v>0.08119444656469808</v>
       </c>
       <c r="H31" t="n">
-        <v>0.790888611533765</v>
+        <v>0.1733462810478448</v>
       </c>
       <c r="I31" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.75047682599171</v>
+      </c>
+      <c r="K31" t="n">
         <v>9</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>15</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.96</v>
-      </c>
       <c r="S31" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T31" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.76</v>
       </c>
       <c r="U31" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.17</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.1233333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2699,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.63</v>
+        <v>0.582</v>
       </c>
     </row>
     <row r="3">
@@ -2699,7 +2709,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.771</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2719,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2719,7 +2729,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.649</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="6">
@@ -2729,7 +2739,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="7">
@@ -2739,7 +2749,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.76</v>
+        <v>0.731</v>
       </c>
     </row>
   </sheetData>
@@ -2815,25 +2825,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.582</v>
       </c>
       <c r="D2" t="n">
-        <v>0.623</v>
+        <v>0.548</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9</v>
+        <v>0.833</v>
       </c>
       <c r="F2" t="n">
-        <v>0.492</v>
+        <v>0.433</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.667</v>
+        <v>0.778</v>
       </c>
       <c r="I2" t="n">
-        <v>0.213</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="3">
@@ -2848,25 +2858,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.747</v>
+        <v>0.575</v>
       </c>
       <c r="E3" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>0.496</v>
       </c>
       <c r="G3" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.227</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="4">
@@ -2881,25 +2891,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.592</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.646</v>
+        <v>0.529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>0.233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.267</v>
+        <v>0.578</v>
       </c>
       <c r="I4" t="n">
-        <v>0.293</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="5">
@@ -2914,25 +2924,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.618</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.833</v>
+        <v>0.733</v>
       </c>
       <c r="F5" t="n">
-        <v>0.607</v>
+        <v>0.548</v>
       </c>
       <c r="G5" t="n">
-        <v>0.167</v>
+        <v>0.267</v>
       </c>
       <c r="H5" t="n">
-        <v>0.422</v>
+        <v>0.578</v>
       </c>
       <c r="I5" t="n">
-        <v>0.218</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="6">
@@ -2947,25 +2957,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.712</v>
       </c>
       <c r="D6" t="n">
-        <v>0.721</v>
+        <v>0.623</v>
       </c>
       <c r="E6" t="n">
-        <v>0.867</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.489</v>
       </c>
       <c r="G6" t="n">
-        <v>0.133</v>
+        <v>0.067</v>
       </c>
       <c r="H6" t="n">
-        <v>0.422</v>
+        <v>0.756</v>
       </c>
       <c r="I6" t="n">
-        <v>0.191</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="7">
@@ -2980,25 +2990,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.731</v>
       </c>
       <c r="D7" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="E7" t="n">
         <v>0.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.677</v>
+        <v>0.54</v>
       </c>
       <c r="G7" t="n">
         <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.267</v>
+        <v>0.578</v>
       </c>
       <c r="I7" t="n">
-        <v>0.213</v>
+        <v>0.276</v>
       </c>
     </row>
   </sheetData>
@@ -3044,7 +3054,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.582</v>
       </c>
     </row>
     <row r="3">
@@ -3054,7 +3064,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="4">
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.673</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3074,7 +3084,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.649</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="6">
@@ -3084,7 +3094,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="7">
@@ -3094,7 +3104,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="8">
@@ -3109,7 +3119,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="9">
@@ -3119,7 +3129,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.923</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10">
@@ -3129,7 +3139,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="11">
@@ -3139,7 +3149,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.867</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="12">
@@ -3149,7 +3159,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="13">
@@ -3159,7 +3169,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.887</v>
+        <v>0.903</v>
       </c>
     </row>
   </sheetData>
